--- a/output/pdf_financials_xlsx/ISO.xlsx
+++ b/output/pdf_financials_xlsx/ISO.xlsx
@@ -3610,10 +3610,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.305937</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.356233</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -10524,7 +10524,11 @@
           <t>Warrant reserve 10</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -10980,7 +10984,11 @@
           <t>Warrant reserve 9</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ISO.xlsx
+++ b/output/pdf_financials_xlsx/ISO.xlsx
@@ -792,28 +792,28 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025391</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.026513</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.056512</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.06666</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.107178</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.747763</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>2.391377</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>1.79273</v>
       </c>
     </row>
     <row r="13">
@@ -1352,28 +1352,28 @@
         <v>-2.835332</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.483037</v>
+        <v>-2.457646</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.832281</v>
+        <v>-1.858794</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.162265</v>
+        <v>-2.218777</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-10.818692</v>
+        <v>-10.885352</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-10.367902</v>
+        <v>-10.47508</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-18.68854</v>
+        <v>-19.436303</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-42.135091</v>
+        <v>-44.526468</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.126399</v>
+        <v>-2.919129</v>
       </c>
     </row>
     <row r="28">
@@ -1420,28 +1420,28 @@
         <v>-2.835332</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.483037</v>
+        <v>-2.457646</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.832281</v>
+        <v>-1.858794</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.162265</v>
+        <v>-2.218777</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-10.818692</v>
+        <v>-10.885352</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-10.367902</v>
+        <v>-10.47508</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-18.68854</v>
+        <v>-19.436303</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-42.135091</v>
+        <v>-44.526468</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.126399</v>
+        <v>-2.919129</v>
       </c>
     </row>
     <row r="30">
@@ -1596,25 +1596,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>6.49146</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.324582</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>6.405256</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>6.587075</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>13.617066</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>19.912788</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>19.912788</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>21.294663</v>
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>6.49146</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.324582</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>6.405256</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>6.587075</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>9.314985</v>
+        <v>22.932051</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>5.774617</v>
+        <v>25.687405</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>5.774617</v>
+        <v>25.687405</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>52.47573</v>
@@ -2072,25 +2072,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.54616</v>
+        <v>0.0547</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.370031</v>
+        <v>0.045449</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.494573</v>
+        <v>0.08931699999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.77132</v>
+        <v>0.184245</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.724319</v>
+        <v>0.107253</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>20.080067</v>
+        <v>0.167279</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>20.080067</v>
+        <v>0.167279</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>6.610424</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
@@ -20115,7 +20115,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -21710,7 +21710,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -22599,7 +22599,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">

--- a/output/pdf_financials_xlsx/ISO.xlsx
+++ b/output/pdf_financials_xlsx/ISO.xlsx
@@ -619,31 +619,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.316649</v>
+        <v>0.774455</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.474979</v>
+        <v>1.165974</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.740391</v>
+        <v>1.472514</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.899367</v>
+        <v>1.598013</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.438374</v>
+        <v>2.575456</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.798936</v>
+        <v>2.211408</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.930795</v>
+        <v>2.552189</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.265727</v>
+        <v>7.385754</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3.378564</v>
+        <v>7.815222</v>
       </c>
     </row>
     <row r="8">
@@ -721,31 +721,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.316649</v>
+        <v>0.774455</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.474979</v>
+        <v>1.165974</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.740391</v>
+        <v>1.472514</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.899367</v>
+        <v>1.598013</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.438374</v>
+        <v>2.575456</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.798936</v>
+        <v>2.211408</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.930795</v>
+        <v>2.552189</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.265727</v>
+        <v>7.385754</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.378564</v>
+        <v>7.815222</v>
       </c>
     </row>
     <row r="11">
@@ -925,31 +925,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2.835332</v>
+        <v>-2.62108</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-2.483037</v>
+        <v>-2.449725</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.832281</v>
+        <v>-1.522983</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-2.162265</v>
+        <v>-2.22731</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-10.818692</v>
+        <v>-11.862652</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-10.367902</v>
+        <v>-9.343158000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-18.68854</v>
+        <v>-16.836397</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-42.135091</v>
+        <v>-40.002292</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.126399</v>
+        <v>2.642854</v>
       </c>
     </row>
     <row r="17">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.290028</v>
+        <v>0.075776</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.033312</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.309298</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.06504500000000001</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>1.04396</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.024744</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.852143</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.132799</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.769253</v>
       </c>
     </row>
     <row r="18">
@@ -1115,10 +1115,10 @@
         <v>-10.367902</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-18.68854</v>
+        <v>-18.670684</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-42.135091</v>
+        <v>-42.006733</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-1.126399</v>
@@ -1349,31 +1349,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.835332</v>
+        <v>-2.62108</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.457646</v>
+        <v>-2.424334</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.858794</v>
+        <v>-1.549496</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.218777</v>
+        <v>-2.283822</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-10.885352</v>
+        <v>-11.929312</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-10.47508</v>
+        <v>-9.450336</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-19.436303</v>
+        <v>-17.58416</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-44.526468</v>
+        <v>-42.393669</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.919129</v>
+        <v>0.850124</v>
       </c>
     </row>
     <row r="28">
@@ -1417,31 +1417,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.835332</v>
+        <v>-2.62108</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.457646</v>
+        <v>-2.424334</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.858794</v>
+        <v>-1.549496</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.218777</v>
+        <v>-2.283822</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-10.885352</v>
+        <v>-11.929312</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-10.47508</v>
+        <v>-9.450336</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-19.436303</v>
+        <v>-17.58416</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-44.526468</v>
+        <v>-42.393669</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.919129</v>
+        <v>0.850124</v>
       </c>
     </row>
     <row r="30">
@@ -1503,31 +1503,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-10.22906664898502</v>
+        <v>-2.891022021456804</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.359826102929921</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-20.30869681408131</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.920338884124797</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-8.800393031844818</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-10.96785476602237</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-11.00082755235577</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.33169199404874</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>142.620553386604</v>
       </c>
     </row>
     <row r="32">
@@ -11647,7 +11647,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -13818,7 +13822,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -18429,7 +18437,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -19226,7 +19238,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E239" s="5" t="n">
         <v>0.290028</v>
       </c>
@@ -19730,7 +19746,11 @@
           <t>Administrative salaries, contractor and director fees 15</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -20705,7 +20725,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -20764,7 +20788,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -21588,7 +21616,11 @@
           <t>Administrative salaries, contractor and director fees 16</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -21950,7 +21982,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -23435,7 +23471,11 @@
           <t>Administrative salaries, contract and director fees 13</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -23791,7 +23831,11 @@
           <t>Deferred income tax recovery/(expense) 11</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -24334,7 +24378,11 @@
           <t>Administrative salaries, contract and director fees 11</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -24576,7 +24624,11 @@
           <t>Deferred income tax recovery (expense) 9</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -24867,7 +24919,11 @@
           <t>Administrative salaries, contract and director fees 10</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -25315,7 +25371,11 @@
           <t>Deferred income tax recovery 8</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -25539,7 +25599,11 @@
           <t>Administrative salaries, contract and director fees</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E346" s="5" t="n">
         <v>0.457806</v>
       </c>
@@ -25763,7 +25827,11 @@
           <t>Deferred income tax recovery(expense) 9</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E350" s="5" t="n">
         <v>-0.075776</v>
       </c>
